--- a/Relaciones totales libro-patrimonio/LIBRO PATRIMONIO INMATERIAL.xlsx
+++ b/Relaciones totales libro-patrimonio/LIBRO PATRIMONIO INMATERIAL.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91CC1AAE-E61F-49E1-95F5-21BB12D4A066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="personalidad y general" sheetId="1" r:id="rId1"/>
@@ -3589,7 +3589,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3756,8 +3756,17 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3813,6 +3822,9 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3822,13 +3834,13 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3840,31 +3852,13 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4186,41 +4180,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="57" t="s">
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="60" t="s">
         <v>137</v>
       </c>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="58"/>
-      <c r="S1" s="58"/>
-      <c r="T1" s="58"/>
-      <c r="U1" s="58"/>
-      <c r="V1" s="58"/>
-      <c r="W1" s="58"/>
-      <c r="X1" s="58"/>
-      <c r="Y1" s="58"/>
-      <c r="Z1" s="58"/>
-      <c r="AA1" s="58"/>
-      <c r="AB1" s="58"/>
-      <c r="AC1" s="58"/>
-      <c r="AD1" s="58"/>
-      <c r="AE1" s="58"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="61"/>
+      <c r="P1" s="61"/>
+      <c r="Q1" s="61"/>
+      <c r="R1" s="61"/>
+      <c r="S1" s="61"/>
+      <c r="T1" s="61"/>
+      <c r="U1" s="61"/>
+      <c r="V1" s="61"/>
+      <c r="W1" s="61"/>
+      <c r="X1" s="61"/>
+      <c r="Y1" s="61"/>
+      <c r="Z1" s="61"/>
+      <c r="AA1" s="61"/>
+      <c r="AB1" s="61"/>
+      <c r="AC1" s="61"/>
+      <c r="AD1" s="61"/>
+      <c r="AE1" s="61"/>
     </row>
     <row r="2" spans="1:31" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -5486,27 +5480,27 @@
       </c>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="G20" s="59" t="s">
+      <c r="G20" s="62" t="s">
         <v>274</v>
       </c>
-      <c r="H20" s="59"/>
-      <c r="I20" s="59"/>
-      <c r="J20" s="59"/>
-      <c r="K20" s="59"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="62"/>
+      <c r="K20" s="62"/>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="G21" s="59"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="59"/>
-      <c r="J21" s="59"/>
-      <c r="K21" s="59"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="62"/>
+      <c r="K21" s="62"/>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="G22" s="59"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="59"/>
-      <c r="J22" s="59"/>
-      <c r="K22" s="59"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5608,32 +5602,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="57" t="s">
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="60" t="s">
         <v>138</v>
       </c>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="58"/>
-      <c r="S1" s="58"/>
-      <c r="T1" s="58"/>
-      <c r="U1" s="58"/>
-      <c r="V1" s="58"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="61"/>
+      <c r="P1" s="61"/>
+      <c r="Q1" s="61"/>
+      <c r="R1" s="61"/>
+      <c r="S1" s="61"/>
+      <c r="T1" s="61"/>
+      <c r="U1" s="61"/>
+      <c r="V1" s="61"/>
       <c r="W1" s="6"/>
       <c r="X1" s="6"/>
       <c r="Y1" s="6"/>
@@ -6002,7 +5996,7 @@
       <c r="P7" s="21"/>
       <c r="Q7" s="21"/>
       <c r="R7" s="22"/>
-      <c r="S7" s="92">
+      <c r="S7" s="59">
         <v>2</v>
       </c>
       <c r="T7" s="21"/>
@@ -6708,20 +6702,20 @@
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="89"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
       <c r="I20" s="6"/>
-      <c r="J20" s="89"/>
+      <c r="J20" s="6"/>
       <c r="K20" s="6"/>
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
-      <c r="N20" s="89"/>
+      <c r="N20" s="6"/>
       <c r="O20" s="6"/>
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
       <c r="S20" s="6"/>
-      <c r="T20" s="89"/>
+      <c r="T20" s="6"/>
       <c r="U20" s="6"/>
       <c r="V20" s="6"/>
       <c r="W20" s="6"/>
@@ -6745,25 +6739,25 @@
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
-      <c r="D21" s="59" t="s">
+      <c r="D21" s="62" t="s">
         <v>268</v>
       </c>
-      <c r="E21" s="59"/>
-      <c r="F21" s="59"/>
-      <c r="G21" s="59"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="59"/>
-      <c r="J21" s="59"/>
-      <c r="K21" s="59"/>
-      <c r="L21" s="59"/>
-      <c r="M21" s="59"/>
-      <c r="N21" s="59"/>
-      <c r="O21" s="59"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="62"/>
+      <c r="K21" s="62"/>
+      <c r="L21" s="62"/>
+      <c r="M21" s="62"/>
+      <c r="N21" s="62"/>
+      <c r="O21" s="62"/>
       <c r="P21" s="6"/>
       <c r="Q21" s="6"/>
       <c r="R21" s="6"/>
       <c r="S21" s="6"/>
-      <c r="T21" s="89"/>
+      <c r="T21" s="6"/>
       <c r="U21" s="6"/>
       <c r="V21" s="6"/>
       <c r="W21" s="6"/>
@@ -6787,23 +6781,23 @@
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="59"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="59"/>
-      <c r="J22" s="59"/>
-      <c r="K22" s="59"/>
-      <c r="L22" s="59"/>
-      <c r="M22" s="59"/>
-      <c r="N22" s="59"/>
-      <c r="O22" s="59"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="62"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="62"/>
+      <c r="O22" s="62"/>
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="6"/>
-      <c r="T22" s="89"/>
+      <c r="T22" s="6"/>
       <c r="U22" s="6"/>
       <c r="V22" s="6"/>
       <c r="W22" s="6"/>
@@ -6827,18 +6821,18 @@
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="59"/>
-      <c r="J23" s="59"/>
-      <c r="K23" s="59"/>
-      <c r="L23" s="59"/>
-      <c r="M23" s="59"/>
-      <c r="N23" s="59"/>
-      <c r="O23" s="59"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="62"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="62"/>
+      <c r="K23" s="62"/>
+      <c r="L23" s="62"/>
+      <c r="M23" s="62"/>
+      <c r="N23" s="62"/>
+      <c r="O23" s="62"/>
       <c r="P23" s="6"/>
       <c r="Q23" s="6"/>
       <c r="R23" s="6"/>
@@ -8363,59 +8357,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:49" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="57" t="s">
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="60" t="s">
         <v>139</v>
       </c>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="58"/>
-      <c r="S1" s="58"/>
-      <c r="T1" s="58"/>
-      <c r="U1" s="58"/>
-      <c r="V1" s="58"/>
-      <c r="W1" s="58"/>
-      <c r="X1" s="58"/>
-      <c r="Y1" s="58"/>
-      <c r="Z1" s="58"/>
-      <c r="AA1" s="58"/>
-      <c r="AB1" s="58"/>
-      <c r="AC1" s="89"/>
-      <c r="AD1" s="89"/>
-      <c r="AE1" s="89"/>
-      <c r="AF1" s="89"/>
-      <c r="AG1" s="89"/>
-      <c r="AH1" s="89"/>
-      <c r="AI1" s="89"/>
-      <c r="AJ1" s="89"/>
-      <c r="AK1" s="89"/>
-      <c r="AL1" s="89"/>
-      <c r="AM1" s="89"/>
-      <c r="AN1" s="89"/>
-      <c r="AO1" s="89"/>
-      <c r="AP1" s="89"/>
-      <c r="AQ1" s="89"/>
-      <c r="AR1" s="89"/>
-      <c r="AS1" s="89"/>
-      <c r="AT1" s="89"/>
-      <c r="AU1" s="89"/>
-      <c r="AV1" s="89"/>
-      <c r="AW1" s="87"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="61"/>
+      <c r="P1" s="61"/>
+      <c r="Q1" s="61"/>
+      <c r="R1" s="61"/>
+      <c r="S1" s="61"/>
+      <c r="T1" s="61"/>
+      <c r="U1" s="61"/>
+      <c r="V1" s="61"/>
+      <c r="W1" s="61"/>
+      <c r="X1" s="61"/>
+      <c r="Y1" s="61"/>
+      <c r="Z1" s="61"/>
+      <c r="AA1" s="61"/>
+      <c r="AB1" s="61"/>
+      <c r="AC1" s="6"/>
+      <c r="AD1" s="6"/>
+      <c r="AE1" s="6"/>
+      <c r="AF1" s="6"/>
+      <c r="AG1" s="6"/>
+      <c r="AH1" s="6"/>
+      <c r="AI1" s="6"/>
+      <c r="AJ1" s="6"/>
+      <c r="AK1" s="6"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AN1" s="6"/>
+      <c r="AO1" s="6"/>
+      <c r="AP1" s="6"/>
+      <c r="AQ1" s="6"/>
+      <c r="AR1" s="6"/>
+      <c r="AS1" s="6"/>
+      <c r="AT1" s="6"/>
+      <c r="AU1" s="6"/>
+      <c r="AV1" s="6"/>
+      <c r="AW1" s="56"/>
     </row>
     <row r="2" spans="1:49" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -8499,30 +8493,30 @@
       <c r="AA2" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="AB2" s="91" t="s">
+      <c r="AB2" s="58" t="s">
         <v>98</v>
       </c>
-      <c r="AC2" s="89"/>
-      <c r="AD2" s="89"/>
-      <c r="AE2" s="89"/>
-      <c r="AF2" s="89"/>
-      <c r="AG2" s="89"/>
-      <c r="AH2" s="89"/>
-      <c r="AI2" s="89"/>
-      <c r="AJ2" s="89"/>
-      <c r="AK2" s="89"/>
-      <c r="AL2" s="89"/>
-      <c r="AM2" s="89"/>
-      <c r="AN2" s="89"/>
-      <c r="AO2" s="89"/>
-      <c r="AP2" s="89"/>
-      <c r="AQ2" s="89"/>
-      <c r="AR2" s="89"/>
-      <c r="AS2" s="89"/>
-      <c r="AT2" s="89"/>
-      <c r="AU2" s="89"/>
-      <c r="AV2" s="89"/>
-      <c r="AW2" s="87"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="6"/>
+      <c r="AH2" s="6"/>
+      <c r="AI2" s="6"/>
+      <c r="AJ2" s="6"/>
+      <c r="AK2" s="6"/>
+      <c r="AL2" s="6"/>
+      <c r="AM2" s="6"/>
+      <c r="AN2" s="6"/>
+      <c r="AO2" s="6"/>
+      <c r="AP2" s="6"/>
+      <c r="AQ2" s="6"/>
+      <c r="AR2" s="6"/>
+      <c r="AS2" s="6"/>
+      <c r="AT2" s="6"/>
+      <c r="AU2" s="6"/>
+      <c r="AV2" s="6"/>
+      <c r="AW2" s="56"/>
     </row>
     <row r="3" spans="1:49" ht="37.200000000000003" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
@@ -8589,27 +8583,27 @@
       <c r="Z3" s="13"/>
       <c r="AA3" s="13"/>
       <c r="AB3" s="14"/>
-      <c r="AC3" s="89"/>
-      <c r="AD3" s="89"/>
-      <c r="AE3" s="89"/>
-      <c r="AF3" s="89"/>
-      <c r="AG3" s="89"/>
-      <c r="AH3" s="89"/>
-      <c r="AI3" s="89"/>
-      <c r="AJ3" s="89"/>
-      <c r="AK3" s="89"/>
-      <c r="AL3" s="89"/>
-      <c r="AM3" s="89"/>
-      <c r="AN3" s="89"/>
-      <c r="AO3" s="89"/>
-      <c r="AP3" s="89"/>
-      <c r="AQ3" s="89"/>
-      <c r="AR3" s="89"/>
-      <c r="AS3" s="89"/>
-      <c r="AT3" s="89"/>
-      <c r="AU3" s="89"/>
-      <c r="AV3" s="89"/>
-      <c r="AW3" s="87"/>
+      <c r="AC3" s="6"/>
+      <c r="AD3" s="6"/>
+      <c r="AE3" s="6"/>
+      <c r="AF3" s="6"/>
+      <c r="AG3" s="6"/>
+      <c r="AH3" s="6"/>
+      <c r="AI3" s="6"/>
+      <c r="AJ3" s="6"/>
+      <c r="AK3" s="6"/>
+      <c r="AL3" s="6"/>
+      <c r="AM3" s="6"/>
+      <c r="AN3" s="6"/>
+      <c r="AO3" s="6"/>
+      <c r="AP3" s="6"/>
+      <c r="AQ3" s="6"/>
+      <c r="AR3" s="6"/>
+      <c r="AS3" s="6"/>
+      <c r="AT3" s="6"/>
+      <c r="AU3" s="6"/>
+      <c r="AV3" s="6"/>
+      <c r="AW3" s="56"/>
     </row>
     <row r="4" spans="1:49" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
@@ -8670,27 +8664,27 @@
       </c>
       <c r="AA4" s="7"/>
       <c r="AB4" s="16"/>
-      <c r="AC4" s="89"/>
-      <c r="AD4" s="89"/>
-      <c r="AE4" s="89"/>
-      <c r="AF4" s="89"/>
-      <c r="AG4" s="89"/>
-      <c r="AH4" s="89"/>
-      <c r="AI4" s="89"/>
-      <c r="AJ4" s="89"/>
-      <c r="AK4" s="89"/>
-      <c r="AL4" s="89"/>
-      <c r="AM4" s="89"/>
-      <c r="AN4" s="89"/>
-      <c r="AO4" s="89"/>
-      <c r="AP4" s="89"/>
-      <c r="AQ4" s="89"/>
-      <c r="AR4" s="89"/>
-      <c r="AS4" s="89"/>
-      <c r="AT4" s="89"/>
-      <c r="AU4" s="89"/>
-      <c r="AV4" s="89"/>
-      <c r="AW4" s="87"/>
+      <c r="AC4" s="6"/>
+      <c r="AD4" s="6"/>
+      <c r="AE4" s="6"/>
+      <c r="AF4" s="6"/>
+      <c r="AG4" s="6"/>
+      <c r="AH4" s="6"/>
+      <c r="AI4" s="6"/>
+      <c r="AJ4" s="6"/>
+      <c r="AK4" s="6"/>
+      <c r="AL4" s="6"/>
+      <c r="AM4" s="6"/>
+      <c r="AN4" s="6"/>
+      <c r="AO4" s="6"/>
+      <c r="AP4" s="6"/>
+      <c r="AQ4" s="6"/>
+      <c r="AR4" s="6"/>
+      <c r="AS4" s="6"/>
+      <c r="AT4" s="6"/>
+      <c r="AU4" s="6"/>
+      <c r="AV4" s="6"/>
+      <c r="AW4" s="56"/>
     </row>
     <row r="5" spans="1:49" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
@@ -8759,27 +8753,27 @@
       <c r="AB5" s="16">
         <v>1</v>
       </c>
-      <c r="AC5" s="89"/>
-      <c r="AD5" s="89"/>
-      <c r="AE5" s="89"/>
-      <c r="AF5" s="89"/>
-      <c r="AG5" s="89"/>
-      <c r="AH5" s="89"/>
-      <c r="AI5" s="89"/>
-      <c r="AJ5" s="89"/>
-      <c r="AK5" s="89"/>
-      <c r="AL5" s="89"/>
-      <c r="AM5" s="89"/>
-      <c r="AN5" s="89"/>
-      <c r="AO5" s="89"/>
-      <c r="AP5" s="89"/>
-      <c r="AQ5" s="89"/>
-      <c r="AR5" s="89"/>
-      <c r="AS5" s="89"/>
-      <c r="AT5" s="89"/>
-      <c r="AU5" s="89"/>
-      <c r="AV5" s="89"/>
-      <c r="AW5" s="87"/>
+      <c r="AC5" s="6"/>
+      <c r="AD5" s="6"/>
+      <c r="AE5" s="6"/>
+      <c r="AF5" s="6"/>
+      <c r="AG5" s="6"/>
+      <c r="AH5" s="6"/>
+      <c r="AI5" s="6"/>
+      <c r="AJ5" s="6"/>
+      <c r="AK5" s="6"/>
+      <c r="AL5" s="6"/>
+      <c r="AM5" s="6"/>
+      <c r="AN5" s="6"/>
+      <c r="AO5" s="6"/>
+      <c r="AP5" s="6"/>
+      <c r="AQ5" s="6"/>
+      <c r="AR5" s="6"/>
+      <c r="AS5" s="6"/>
+      <c r="AT5" s="6"/>
+      <c r="AU5" s="6"/>
+      <c r="AV5" s="6"/>
+      <c r="AW5" s="56"/>
     </row>
     <row r="6" spans="1:49" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
@@ -8838,27 +8832,27 @@
       <c r="Z6" s="7"/>
       <c r="AA6" s="7"/>
       <c r="AB6" s="16"/>
-      <c r="AC6" s="89"/>
-      <c r="AD6" s="89"/>
-      <c r="AE6" s="89"/>
-      <c r="AF6" s="89"/>
-      <c r="AG6" s="89"/>
-      <c r="AH6" s="89"/>
-      <c r="AI6" s="89"/>
-      <c r="AJ6" s="89"/>
-      <c r="AK6" s="89"/>
-      <c r="AL6" s="89"/>
-      <c r="AM6" s="89"/>
-      <c r="AN6" s="89"/>
-      <c r="AO6" s="89"/>
-      <c r="AP6" s="89"/>
-      <c r="AQ6" s="89"/>
-      <c r="AR6" s="89"/>
-      <c r="AS6" s="89"/>
-      <c r="AT6" s="89"/>
-      <c r="AU6" s="89"/>
-      <c r="AV6" s="89"/>
-      <c r="AW6" s="87"/>
+      <c r="AC6" s="6"/>
+      <c r="AD6" s="6"/>
+      <c r="AE6" s="6"/>
+      <c r="AF6" s="6"/>
+      <c r="AG6" s="6"/>
+      <c r="AH6" s="6"/>
+      <c r="AI6" s="6"/>
+      <c r="AJ6" s="6"/>
+      <c r="AK6" s="6"/>
+      <c r="AL6" s="6"/>
+      <c r="AM6" s="6"/>
+      <c r="AN6" s="6"/>
+      <c r="AO6" s="6"/>
+      <c r="AP6" s="6"/>
+      <c r="AQ6" s="6"/>
+      <c r="AR6" s="6"/>
+      <c r="AS6" s="6"/>
+      <c r="AT6" s="6"/>
+      <c r="AU6" s="6"/>
+      <c r="AV6" s="6"/>
+      <c r="AW6" s="56"/>
     </row>
     <row r="7" spans="1:49" ht="33.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="17" t="s">
@@ -8929,27 +8923,27 @@
       <c r="Z7" s="21"/>
       <c r="AA7" s="21"/>
       <c r="AB7" s="22"/>
-      <c r="AC7" s="89"/>
-      <c r="AD7" s="89"/>
-      <c r="AE7" s="89"/>
-      <c r="AF7" s="89"/>
-      <c r="AG7" s="89"/>
-      <c r="AH7" s="89"/>
-      <c r="AI7" s="89"/>
-      <c r="AJ7" s="89"/>
-      <c r="AK7" s="89"/>
-      <c r="AL7" s="89"/>
-      <c r="AM7" s="89"/>
-      <c r="AN7" s="89"/>
-      <c r="AO7" s="89"/>
-      <c r="AP7" s="89"/>
-      <c r="AQ7" s="89"/>
-      <c r="AR7" s="89"/>
-      <c r="AS7" s="89"/>
-      <c r="AT7" s="89"/>
-      <c r="AU7" s="89"/>
-      <c r="AV7" s="89"/>
-      <c r="AW7" s="87"/>
+      <c r="AC7" s="6"/>
+      <c r="AD7" s="6"/>
+      <c r="AE7" s="6"/>
+      <c r="AF7" s="6"/>
+      <c r="AG7" s="6"/>
+      <c r="AH7" s="6"/>
+      <c r="AI7" s="6"/>
+      <c r="AJ7" s="6"/>
+      <c r="AK7" s="6"/>
+      <c r="AL7" s="6"/>
+      <c r="AM7" s="6"/>
+      <c r="AN7" s="6"/>
+      <c r="AO7" s="6"/>
+      <c r="AP7" s="6"/>
+      <c r="AQ7" s="6"/>
+      <c r="AR7" s="6"/>
+      <c r="AS7" s="6"/>
+      <c r="AT7" s="6"/>
+      <c r="AU7" s="6"/>
+      <c r="AV7" s="6"/>
+      <c r="AW7" s="56"/>
     </row>
     <row r="8" spans="1:49" ht="35.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A8" s="23" t="s">
@@ -9012,27 +9006,27 @@
         <v>1</v>
       </c>
       <c r="AB8" s="35"/>
-      <c r="AC8" s="89"/>
-      <c r="AD8" s="89"/>
-      <c r="AE8" s="89"/>
-      <c r="AF8" s="89"/>
-      <c r="AG8" s="89"/>
-      <c r="AH8" s="89"/>
-      <c r="AI8" s="89"/>
-      <c r="AJ8" s="89"/>
-      <c r="AK8" s="89"/>
-      <c r="AL8" s="89"/>
-      <c r="AM8" s="89"/>
-      <c r="AN8" s="89"/>
-      <c r="AO8" s="89"/>
-      <c r="AP8" s="89"/>
-      <c r="AQ8" s="89"/>
-      <c r="AR8" s="89"/>
-      <c r="AS8" s="89"/>
-      <c r="AT8" s="89"/>
-      <c r="AU8" s="89"/>
-      <c r="AV8" s="89"/>
-      <c r="AW8" s="87"/>
+      <c r="AC8" s="6"/>
+      <c r="AD8" s="6"/>
+      <c r="AE8" s="6"/>
+      <c r="AF8" s="6"/>
+      <c r="AG8" s="6"/>
+      <c r="AH8" s="6"/>
+      <c r="AI8" s="6"/>
+      <c r="AJ8" s="6"/>
+      <c r="AK8" s="6"/>
+      <c r="AL8" s="6"/>
+      <c r="AM8" s="6"/>
+      <c r="AN8" s="6"/>
+      <c r="AO8" s="6"/>
+      <c r="AP8" s="6"/>
+      <c r="AQ8" s="6"/>
+      <c r="AR8" s="6"/>
+      <c r="AS8" s="6"/>
+      <c r="AT8" s="6"/>
+      <c r="AU8" s="6"/>
+      <c r="AV8" s="6"/>
+      <c r="AW8" s="56"/>
     </row>
     <row r="9" spans="1:49" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
@@ -9097,27 +9091,27 @@
       </c>
       <c r="AA9" s="7"/>
       <c r="AB9" s="16"/>
-      <c r="AC9" s="89"/>
-      <c r="AD9" s="89"/>
-      <c r="AE9" s="89"/>
-      <c r="AF9" s="89"/>
-      <c r="AG9" s="89"/>
-      <c r="AH9" s="89"/>
-      <c r="AI9" s="89"/>
-      <c r="AJ9" s="89"/>
-      <c r="AK9" s="89"/>
-      <c r="AL9" s="89"/>
-      <c r="AM9" s="89"/>
-      <c r="AN9" s="89"/>
-      <c r="AO9" s="89"/>
-      <c r="AP9" s="89"/>
-      <c r="AQ9" s="89"/>
-      <c r="AR9" s="89"/>
-      <c r="AS9" s="89"/>
-      <c r="AT9" s="89"/>
-      <c r="AU9" s="89"/>
-      <c r="AV9" s="89"/>
-      <c r="AW9" s="87"/>
+      <c r="AC9" s="6"/>
+      <c r="AD9" s="6"/>
+      <c r="AE9" s="6"/>
+      <c r="AF9" s="6"/>
+      <c r="AG9" s="6"/>
+      <c r="AH9" s="6"/>
+      <c r="AI9" s="6"/>
+      <c r="AJ9" s="6"/>
+      <c r="AK9" s="6"/>
+      <c r="AL9" s="6"/>
+      <c r="AM9" s="6"/>
+      <c r="AN9" s="6"/>
+      <c r="AO9" s="6"/>
+      <c r="AP9" s="6"/>
+      <c r="AQ9" s="6"/>
+      <c r="AR9" s="6"/>
+      <c r="AS9" s="6"/>
+      <c r="AT9" s="6"/>
+      <c r="AU9" s="6"/>
+      <c r="AV9" s="6"/>
+      <c r="AW9" s="56"/>
     </row>
     <row r="10" spans="1:49" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -9174,27 +9168,27 @@
       <c r="Z10" s="7"/>
       <c r="AA10" s="7"/>
       <c r="AB10" s="16"/>
-      <c r="AC10" s="89"/>
-      <c r="AD10" s="89"/>
-      <c r="AE10" s="89"/>
-      <c r="AF10" s="89"/>
-      <c r="AG10" s="89"/>
-      <c r="AH10" s="89"/>
-      <c r="AI10" s="89"/>
-      <c r="AJ10" s="89"/>
-      <c r="AK10" s="89"/>
-      <c r="AL10" s="89"/>
-      <c r="AM10" s="89"/>
-      <c r="AN10" s="89"/>
-      <c r="AO10" s="89"/>
-      <c r="AP10" s="89"/>
-      <c r="AQ10" s="89"/>
-      <c r="AR10" s="89"/>
-      <c r="AS10" s="89"/>
-      <c r="AT10" s="89"/>
-      <c r="AU10" s="89"/>
-      <c r="AV10" s="89"/>
-      <c r="AW10" s="87"/>
+      <c r="AC10" s="6"/>
+      <c r="AD10" s="6"/>
+      <c r="AE10" s="6"/>
+      <c r="AF10" s="6"/>
+      <c r="AG10" s="6"/>
+      <c r="AH10" s="6"/>
+      <c r="AI10" s="6"/>
+      <c r="AJ10" s="6"/>
+      <c r="AK10" s="6"/>
+      <c r="AL10" s="6"/>
+      <c r="AM10" s="6"/>
+      <c r="AN10" s="6"/>
+      <c r="AO10" s="6"/>
+      <c r="AP10" s="6"/>
+      <c r="AQ10" s="6"/>
+      <c r="AR10" s="6"/>
+      <c r="AS10" s="6"/>
+      <c r="AT10" s="6"/>
+      <c r="AU10" s="6"/>
+      <c r="AV10" s="6"/>
+      <c r="AW10" s="56"/>
     </row>
     <row r="11" spans="1:49" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
@@ -9245,27 +9239,27 @@
       <c r="Z11" s="7"/>
       <c r="AA11" s="7"/>
       <c r="AB11" s="16"/>
-      <c r="AC11" s="89"/>
-      <c r="AD11" s="89"/>
-      <c r="AE11" s="89"/>
-      <c r="AF11" s="89"/>
-      <c r="AG11" s="89"/>
-      <c r="AH11" s="89"/>
-      <c r="AI11" s="89"/>
-      <c r="AJ11" s="89"/>
-      <c r="AK11" s="89"/>
-      <c r="AL11" s="89"/>
-      <c r="AM11" s="89"/>
-      <c r="AN11" s="89"/>
-      <c r="AO11" s="89"/>
-      <c r="AP11" s="89"/>
-      <c r="AQ11" s="89"/>
-      <c r="AR11" s="89"/>
-      <c r="AS11" s="89"/>
-      <c r="AT11" s="89"/>
-      <c r="AU11" s="89"/>
-      <c r="AV11" s="89"/>
-      <c r="AW11" s="87"/>
+      <c r="AC11" s="6"/>
+      <c r="AD11" s="6"/>
+      <c r="AE11" s="6"/>
+      <c r="AF11" s="6"/>
+      <c r="AG11" s="6"/>
+      <c r="AH11" s="6"/>
+      <c r="AI11" s="6"/>
+      <c r="AJ11" s="6"/>
+      <c r="AK11" s="6"/>
+      <c r="AL11" s="6"/>
+      <c r="AM11" s="6"/>
+      <c r="AN11" s="6"/>
+      <c r="AO11" s="6"/>
+      <c r="AP11" s="6"/>
+      <c r="AQ11" s="6"/>
+      <c r="AR11" s="6"/>
+      <c r="AS11" s="6"/>
+      <c r="AT11" s="6"/>
+      <c r="AU11" s="6"/>
+      <c r="AV11" s="6"/>
+      <c r="AW11" s="56"/>
     </row>
     <row r="12" spans="1:49" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
@@ -9326,27 +9320,27 @@
       <c r="Z12" s="7"/>
       <c r="AA12" s="7"/>
       <c r="AB12" s="16"/>
-      <c r="AC12" s="89"/>
-      <c r="AD12" s="89"/>
-      <c r="AE12" s="89"/>
-      <c r="AF12" s="89"/>
-      <c r="AG12" s="89"/>
-      <c r="AH12" s="89"/>
-      <c r="AI12" s="89"/>
-      <c r="AJ12" s="89"/>
-      <c r="AK12" s="89"/>
-      <c r="AL12" s="89"/>
-      <c r="AM12" s="89"/>
-      <c r="AN12" s="89"/>
-      <c r="AO12" s="89"/>
-      <c r="AP12" s="89"/>
-      <c r="AQ12" s="89"/>
-      <c r="AR12" s="89"/>
-      <c r="AS12" s="89"/>
-      <c r="AT12" s="89"/>
-      <c r="AU12" s="89"/>
-      <c r="AV12" s="89"/>
-      <c r="AW12" s="87"/>
+      <c r="AC12" s="6"/>
+      <c r="AD12" s="6"/>
+      <c r="AE12" s="6"/>
+      <c r="AF12" s="6"/>
+      <c r="AG12" s="6"/>
+      <c r="AH12" s="6"/>
+      <c r="AI12" s="6"/>
+      <c r="AJ12" s="6"/>
+      <c r="AK12" s="6"/>
+      <c r="AL12" s="6"/>
+      <c r="AM12" s="6"/>
+      <c r="AN12" s="6"/>
+      <c r="AO12" s="6"/>
+      <c r="AP12" s="6"/>
+      <c r="AQ12" s="6"/>
+      <c r="AR12" s="6"/>
+      <c r="AS12" s="6"/>
+      <c r="AT12" s="6"/>
+      <c r="AU12" s="6"/>
+      <c r="AV12" s="6"/>
+      <c r="AW12" s="56"/>
     </row>
     <row r="13" spans="1:49" ht="32.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="27" t="s">
@@ -9405,27 +9399,27 @@
       <c r="Z13" s="31"/>
       <c r="AA13" s="21"/>
       <c r="AB13" s="32"/>
-      <c r="AC13" s="89"/>
-      <c r="AD13" s="89"/>
-      <c r="AE13" s="89"/>
-      <c r="AF13" s="89"/>
-      <c r="AG13" s="89"/>
-      <c r="AH13" s="89"/>
-      <c r="AI13" s="89"/>
-      <c r="AJ13" s="89"/>
-      <c r="AK13" s="89"/>
-      <c r="AL13" s="89"/>
-      <c r="AM13" s="89"/>
-      <c r="AN13" s="89"/>
-      <c r="AO13" s="89"/>
-      <c r="AP13" s="89"/>
-      <c r="AQ13" s="89"/>
-      <c r="AR13" s="89"/>
-      <c r="AS13" s="89"/>
-      <c r="AT13" s="89"/>
-      <c r="AU13" s="89"/>
-      <c r="AV13" s="89"/>
-      <c r="AW13" s="87"/>
+      <c r="AC13" s="6"/>
+      <c r="AD13" s="6"/>
+      <c r="AE13" s="6"/>
+      <c r="AF13" s="6"/>
+      <c r="AG13" s="6"/>
+      <c r="AH13" s="6"/>
+      <c r="AI13" s="6"/>
+      <c r="AJ13" s="6"/>
+      <c r="AK13" s="6"/>
+      <c r="AL13" s="6"/>
+      <c r="AM13" s="6"/>
+      <c r="AN13" s="6"/>
+      <c r="AO13" s="6"/>
+      <c r="AP13" s="6"/>
+      <c r="AQ13" s="6"/>
+      <c r="AR13" s="6"/>
+      <c r="AS13" s="6"/>
+      <c r="AT13" s="6"/>
+      <c r="AU13" s="6"/>
+      <c r="AV13" s="6"/>
+      <c r="AW13" s="56"/>
     </row>
     <row r="14" spans="1:49" ht="32.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A14" s="33" t="s">
@@ -9500,27 +9494,27 @@
       <c r="AB14" s="35">
         <v>1</v>
       </c>
-      <c r="AC14" s="89"/>
-      <c r="AD14" s="89"/>
-      <c r="AE14" s="89"/>
-      <c r="AF14" s="89"/>
-      <c r="AG14" s="89"/>
-      <c r="AH14" s="89"/>
-      <c r="AI14" s="89"/>
-      <c r="AJ14" s="89"/>
-      <c r="AK14" s="89"/>
-      <c r="AL14" s="89"/>
-      <c r="AM14" s="89"/>
-      <c r="AN14" s="89"/>
-      <c r="AO14" s="89"/>
-      <c r="AP14" s="89"/>
-      <c r="AQ14" s="89"/>
-      <c r="AR14" s="89"/>
-      <c r="AS14" s="89"/>
-      <c r="AT14" s="89"/>
-      <c r="AU14" s="89"/>
-      <c r="AV14" s="89"/>
-      <c r="AW14" s="87"/>
+      <c r="AC14" s="6"/>
+      <c r="AD14" s="6"/>
+      <c r="AE14" s="6"/>
+      <c r="AF14" s="6"/>
+      <c r="AG14" s="6"/>
+      <c r="AH14" s="6"/>
+      <c r="AI14" s="6"/>
+      <c r="AJ14" s="6"/>
+      <c r="AK14" s="6"/>
+      <c r="AL14" s="6"/>
+      <c r="AM14" s="6"/>
+      <c r="AN14" s="6"/>
+      <c r="AO14" s="6"/>
+      <c r="AP14" s="6"/>
+      <c r="AQ14" s="6"/>
+      <c r="AR14" s="6"/>
+      <c r="AS14" s="6"/>
+      <c r="AT14" s="6"/>
+      <c r="AU14" s="6"/>
+      <c r="AV14" s="6"/>
+      <c r="AW14" s="56"/>
     </row>
     <row r="15" spans="1:49" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
@@ -9581,27 +9575,27 @@
       <c r="Z15" s="7"/>
       <c r="AA15" s="7"/>
       <c r="AB15" s="16"/>
-      <c r="AC15" s="89"/>
-      <c r="AD15" s="89"/>
-      <c r="AE15" s="89"/>
-      <c r="AF15" s="89"/>
-      <c r="AG15" s="89"/>
-      <c r="AH15" s="89"/>
-      <c r="AI15" s="89"/>
-      <c r="AJ15" s="89"/>
-      <c r="AK15" s="89"/>
-      <c r="AL15" s="89"/>
-      <c r="AM15" s="89"/>
-      <c r="AN15" s="89"/>
-      <c r="AO15" s="89"/>
-      <c r="AP15" s="89"/>
-      <c r="AQ15" s="89"/>
-      <c r="AR15" s="89"/>
-      <c r="AS15" s="89"/>
-      <c r="AT15" s="89"/>
-      <c r="AU15" s="89"/>
-      <c r="AV15" s="89"/>
-      <c r="AW15" s="87"/>
+      <c r="AC15" s="6"/>
+      <c r="AD15" s="6"/>
+      <c r="AE15" s="6"/>
+      <c r="AF15" s="6"/>
+      <c r="AG15" s="6"/>
+      <c r="AH15" s="6"/>
+      <c r="AI15" s="6"/>
+      <c r="AJ15" s="6"/>
+      <c r="AK15" s="6"/>
+      <c r="AL15" s="6"/>
+      <c r="AM15" s="6"/>
+      <c r="AN15" s="6"/>
+      <c r="AO15" s="6"/>
+      <c r="AP15" s="6"/>
+      <c r="AQ15" s="6"/>
+      <c r="AR15" s="6"/>
+      <c r="AS15" s="6"/>
+      <c r="AT15" s="6"/>
+      <c r="AU15" s="6"/>
+      <c r="AV15" s="6"/>
+      <c r="AW15" s="56"/>
     </row>
     <row r="16" spans="1:49" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
@@ -9674,27 +9668,27 @@
       <c r="Z16" s="7"/>
       <c r="AA16" s="7"/>
       <c r="AB16" s="16"/>
-      <c r="AC16" s="89"/>
-      <c r="AD16" s="89"/>
-      <c r="AE16" s="89"/>
-      <c r="AF16" s="89"/>
-      <c r="AG16" s="89"/>
-      <c r="AH16" s="89"/>
-      <c r="AI16" s="89"/>
-      <c r="AJ16" s="89"/>
-      <c r="AK16" s="89"/>
-      <c r="AL16" s="89"/>
-      <c r="AM16" s="89"/>
-      <c r="AN16" s="89"/>
-      <c r="AO16" s="89"/>
-      <c r="AP16" s="89"/>
-      <c r="AQ16" s="89"/>
-      <c r="AR16" s="89"/>
-      <c r="AS16" s="89"/>
-      <c r="AT16" s="89"/>
-      <c r="AU16" s="89"/>
-      <c r="AV16" s="89"/>
-      <c r="AW16" s="87"/>
+      <c r="AC16" s="6"/>
+      <c r="AD16" s="6"/>
+      <c r="AE16" s="6"/>
+      <c r="AF16" s="6"/>
+      <c r="AG16" s="6"/>
+      <c r="AH16" s="6"/>
+      <c r="AI16" s="6"/>
+      <c r="AJ16" s="6"/>
+      <c r="AK16" s="6"/>
+      <c r="AL16" s="6"/>
+      <c r="AM16" s="6"/>
+      <c r="AN16" s="6"/>
+      <c r="AO16" s="6"/>
+      <c r="AP16" s="6"/>
+      <c r="AQ16" s="6"/>
+      <c r="AR16" s="6"/>
+      <c r="AS16" s="6"/>
+      <c r="AT16" s="6"/>
+      <c r="AU16" s="6"/>
+      <c r="AV16" s="6"/>
+      <c r="AW16" s="56"/>
     </row>
     <row r="17" spans="1:49" ht="30.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="17" t="s">
@@ -9751,27 +9745,27 @@
       <c r="Z17" s="21"/>
       <c r="AA17" s="21"/>
       <c r="AB17" s="22"/>
-      <c r="AC17" s="89"/>
-      <c r="AD17" s="89"/>
-      <c r="AE17" s="89"/>
-      <c r="AF17" s="89"/>
-      <c r="AG17" s="89"/>
-      <c r="AH17" s="89"/>
-      <c r="AI17" s="89"/>
-      <c r="AJ17" s="89"/>
-      <c r="AK17" s="89"/>
-      <c r="AL17" s="89"/>
-      <c r="AM17" s="89"/>
-      <c r="AN17" s="89"/>
-      <c r="AO17" s="89"/>
-      <c r="AP17" s="89"/>
-      <c r="AQ17" s="89"/>
-      <c r="AR17" s="89"/>
-      <c r="AS17" s="89"/>
-      <c r="AT17" s="89"/>
-      <c r="AU17" s="89"/>
-      <c r="AV17" s="89"/>
-      <c r="AW17" s="87"/>
+      <c r="AC17" s="6"/>
+      <c r="AD17" s="6"/>
+      <c r="AE17" s="6"/>
+      <c r="AF17" s="6"/>
+      <c r="AG17" s="6"/>
+      <c r="AH17" s="6"/>
+      <c r="AI17" s="6"/>
+      <c r="AJ17" s="6"/>
+      <c r="AK17" s="6"/>
+      <c r="AL17" s="6"/>
+      <c r="AM17" s="6"/>
+      <c r="AN17" s="6"/>
+      <c r="AO17" s="6"/>
+      <c r="AP17" s="6"/>
+      <c r="AQ17" s="6"/>
+      <c r="AR17" s="6"/>
+      <c r="AS17" s="6"/>
+      <c r="AT17" s="6"/>
+      <c r="AU17" s="6"/>
+      <c r="AV17" s="6"/>
+      <c r="AW17" s="56"/>
     </row>
     <row r="18" spans="1:49" ht="36.6" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A18" s="37"/>
@@ -9780,13 +9774,13 @@
       <c r="D18" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="E18" s="88">
+      <c r="E18" s="57">
         <v>1146</v>
       </c>
-      <c r="F18" s="88">
+      <c r="F18" s="57">
         <v>796</v>
       </c>
-      <c r="G18" s="88">
+      <c r="G18" s="57">
         <v>563</v>
       </c>
       <c r="H18" s="48">
@@ -9795,10 +9789,10 @@
       <c r="I18" s="48">
         <v>119</v>
       </c>
-      <c r="J18" s="88">
+      <c r="J18" s="57">
         <v>108</v>
       </c>
-      <c r="K18" s="88">
+      <c r="K18" s="57">
         <v>50</v>
       </c>
       <c r="L18" s="48">
@@ -9807,7 +9801,7 @@
       <c r="M18" s="48">
         <v>43</v>
       </c>
-      <c r="N18" s="88">
+      <c r="N18" s="57">
         <v>38</v>
       </c>
       <c r="O18" s="48">
@@ -9852,743 +9846,743 @@
       <c r="AB18" s="52">
         <v>1</v>
       </c>
-      <c r="AC18" s="89"/>
-      <c r="AD18" s="89"/>
-      <c r="AE18" s="89"/>
-      <c r="AF18" s="89"/>
-      <c r="AG18" s="89"/>
-      <c r="AH18" s="89"/>
-      <c r="AI18" s="89"/>
-      <c r="AJ18" s="89"/>
-      <c r="AK18" s="89"/>
-      <c r="AL18" s="89"/>
-      <c r="AM18" s="89"/>
-      <c r="AN18" s="89"/>
-      <c r="AO18" s="89"/>
-      <c r="AP18" s="89"/>
-      <c r="AQ18" s="89"/>
-      <c r="AR18" s="89"/>
-      <c r="AS18" s="89"/>
-      <c r="AT18" s="89"/>
-      <c r="AU18" s="89"/>
-      <c r="AV18" s="89"/>
-      <c r="AW18" s="87"/>
+      <c r="AC18" s="6"/>
+      <c r="AD18" s="6"/>
+      <c r="AE18" s="6"/>
+      <c r="AF18" s="6"/>
+      <c r="AG18" s="6"/>
+      <c r="AH18" s="6"/>
+      <c r="AI18" s="6"/>
+      <c r="AJ18" s="6"/>
+      <c r="AK18" s="6"/>
+      <c r="AL18" s="6"/>
+      <c r="AM18" s="6"/>
+      <c r="AN18" s="6"/>
+      <c r="AO18" s="6"/>
+      <c r="AP18" s="6"/>
+      <c r="AQ18" s="6"/>
+      <c r="AR18" s="6"/>
+      <c r="AS18" s="6"/>
+      <c r="AT18" s="6"/>
+      <c r="AU18" s="6"/>
+      <c r="AV18" s="6"/>
+      <c r="AW18" s="56"/>
     </row>
     <row r="19" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A19" s="89"/>
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="89"/>
-      <c r="K19" s="89"/>
-      <c r="L19" s="89"/>
-      <c r="M19" s="89"/>
-      <c r="N19" s="89"/>
-      <c r="O19" s="89"/>
-      <c r="P19" s="89"/>
-      <c r="Q19" s="89"/>
-      <c r="R19" s="89"/>
-      <c r="S19" s="89"/>
-      <c r="T19" s="89"/>
-      <c r="U19" s="89"/>
-      <c r="V19" s="89"/>
-      <c r="W19" s="89"/>
-      <c r="X19" s="89"/>
-      <c r="Y19" s="89"/>
-      <c r="Z19" s="89"/>
-      <c r="AA19" s="89"/>
-      <c r="AB19" s="89"/>
-      <c r="AC19" s="89"/>
-      <c r="AD19" s="89"/>
-      <c r="AE19" s="89"/>
-      <c r="AF19" s="89"/>
-      <c r="AG19" s="89"/>
-      <c r="AH19" s="89"/>
-      <c r="AI19" s="89"/>
-      <c r="AJ19" s="89"/>
-      <c r="AK19" s="89"/>
-      <c r="AL19" s="89"/>
-      <c r="AM19" s="89"/>
-      <c r="AN19" s="89"/>
-      <c r="AO19" s="89"/>
-      <c r="AP19" s="89"/>
-      <c r="AQ19" s="89"/>
-      <c r="AR19" s="89"/>
-      <c r="AS19" s="89"/>
-      <c r="AT19" s="89"/>
-      <c r="AU19" s="89"/>
-      <c r="AV19" s="89"/>
-      <c r="AW19" s="87"/>
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="6"/>
+      <c r="R19" s="6"/>
+      <c r="S19" s="6"/>
+      <c r="T19" s="6"/>
+      <c r="U19" s="6"/>
+      <c r="V19" s="6"/>
+      <c r="W19" s="6"/>
+      <c r="X19" s="6"/>
+      <c r="Y19" s="6"/>
+      <c r="Z19" s="6"/>
+      <c r="AA19" s="6"/>
+      <c r="AB19" s="6"/>
+      <c r="AC19" s="6"/>
+      <c r="AD19" s="6"/>
+      <c r="AE19" s="6"/>
+      <c r="AF19" s="6"/>
+      <c r="AG19" s="6"/>
+      <c r="AH19" s="6"/>
+      <c r="AI19" s="6"/>
+      <c r="AJ19" s="6"/>
+      <c r="AK19" s="6"/>
+      <c r="AL19" s="6"/>
+      <c r="AM19" s="6"/>
+      <c r="AN19" s="6"/>
+      <c r="AO19" s="6"/>
+      <c r="AP19" s="6"/>
+      <c r="AQ19" s="6"/>
+      <c r="AR19" s="6"/>
+      <c r="AS19" s="6"/>
+      <c r="AT19" s="6"/>
+      <c r="AU19" s="6"/>
+      <c r="AV19" s="6"/>
+      <c r="AW19" s="56"/>
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A20" s="89"/>
-      <c r="B20" s="89"/>
-      <c r="C20" s="89"/>
-      <c r="D20" s="89"/>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="90" t="s">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="62" t="s">
         <v>275</v>
       </c>
-      <c r="I20" s="90"/>
-      <c r="J20" s="90"/>
-      <c r="K20" s="90"/>
-      <c r="L20" s="90"/>
-      <c r="M20" s="90"/>
-      <c r="N20" s="89"/>
-      <c r="O20" s="89"/>
-      <c r="P20" s="89"/>
-      <c r="Q20" s="89"/>
-      <c r="R20" s="89"/>
-      <c r="S20" s="89"/>
-      <c r="T20" s="89"/>
-      <c r="U20" s="89"/>
-      <c r="V20" s="89"/>
-      <c r="W20" s="89"/>
-      <c r="X20" s="89"/>
-      <c r="Y20" s="89"/>
-      <c r="Z20" s="89"/>
-      <c r="AA20" s="89"/>
-      <c r="AB20" s="89"/>
-      <c r="AC20" s="89"/>
-      <c r="AD20" s="89"/>
-      <c r="AE20" s="89"/>
-      <c r="AF20" s="89"/>
-      <c r="AG20" s="89"/>
-      <c r="AH20" s="89"/>
-      <c r="AI20" s="89"/>
-      <c r="AJ20" s="89"/>
-      <c r="AK20" s="89"/>
-      <c r="AL20" s="89"/>
-      <c r="AM20" s="89"/>
-      <c r="AN20" s="89"/>
-      <c r="AO20" s="89"/>
-      <c r="AP20" s="89"/>
-      <c r="AQ20" s="89"/>
-      <c r="AR20" s="89"/>
-      <c r="AS20" s="89"/>
-      <c r="AT20" s="89"/>
-      <c r="AU20" s="89"/>
-      <c r="AV20" s="89"/>
-      <c r="AW20" s="87"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="62"/>
+      <c r="K20" s="62"/>
+      <c r="L20" s="62"/>
+      <c r="M20" s="62"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="6"/>
+      <c r="R20" s="6"/>
+      <c r="S20" s="6"/>
+      <c r="T20" s="6"/>
+      <c r="U20" s="6"/>
+      <c r="V20" s="6"/>
+      <c r="W20" s="6"/>
+      <c r="X20" s="6"/>
+      <c r="Y20" s="6"/>
+      <c r="Z20" s="6"/>
+      <c r="AA20" s="6"/>
+      <c r="AB20" s="6"/>
+      <c r="AC20" s="6"/>
+      <c r="AD20" s="6"/>
+      <c r="AE20" s="6"/>
+      <c r="AF20" s="6"/>
+      <c r="AG20" s="6"/>
+      <c r="AH20" s="6"/>
+      <c r="AI20" s="6"/>
+      <c r="AJ20" s="6"/>
+      <c r="AK20" s="6"/>
+      <c r="AL20" s="6"/>
+      <c r="AM20" s="6"/>
+      <c r="AN20" s="6"/>
+      <c r="AO20" s="6"/>
+      <c r="AP20" s="6"/>
+      <c r="AQ20" s="6"/>
+      <c r="AR20" s="6"/>
+      <c r="AS20" s="6"/>
+      <c r="AT20" s="6"/>
+      <c r="AU20" s="6"/>
+      <c r="AV20" s="6"/>
+      <c r="AW20" s="56"/>
     </row>
     <row r="21" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A21" s="89"/>
-      <c r="B21" s="89"/>
-      <c r="C21" s="89"/>
-      <c r="D21" s="89"/>
-      <c r="E21" s="89"/>
-      <c r="F21" s="89"/>
-      <c r="G21" s="89"/>
-      <c r="H21" s="90"/>
-      <c r="I21" s="90"/>
-      <c r="J21" s="90"/>
-      <c r="K21" s="90"/>
-      <c r="L21" s="90"/>
-      <c r="M21" s="90"/>
-      <c r="N21" s="89"/>
-      <c r="O21" s="89"/>
-      <c r="P21" s="89"/>
-      <c r="Q21" s="89"/>
-      <c r="R21" s="89"/>
-      <c r="S21" s="89"/>
-      <c r="T21" s="89"/>
-      <c r="U21" s="89"/>
-      <c r="V21" s="89"/>
-      <c r="W21" s="89"/>
-      <c r="X21" s="89"/>
-      <c r="Y21" s="89"/>
-      <c r="Z21" s="89"/>
-      <c r="AA21" s="89"/>
-      <c r="AB21" s="89"/>
-      <c r="AC21" s="89"/>
-      <c r="AD21" s="89"/>
-      <c r="AE21" s="89"/>
-      <c r="AF21" s="89"/>
-      <c r="AG21" s="89"/>
-      <c r="AH21" s="89"/>
-      <c r="AI21" s="89"/>
-      <c r="AJ21" s="89"/>
-      <c r="AK21" s="89"/>
-      <c r="AL21" s="89"/>
-      <c r="AM21" s="89"/>
-      <c r="AN21" s="89"/>
-      <c r="AO21" s="89"/>
-      <c r="AP21" s="89"/>
-      <c r="AQ21" s="89"/>
-      <c r="AR21" s="89"/>
-      <c r="AS21" s="89"/>
-      <c r="AT21" s="89"/>
-      <c r="AU21" s="89"/>
-      <c r="AV21" s="89"/>
-      <c r="AW21" s="87"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="62"/>
+      <c r="K21" s="62"/>
+      <c r="L21" s="62"/>
+      <c r="M21" s="62"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6"/>
+      <c r="Q21" s="6"/>
+      <c r="R21" s="6"/>
+      <c r="S21" s="6"/>
+      <c r="T21" s="6"/>
+      <c r="U21" s="6"/>
+      <c r="V21" s="6"/>
+      <c r="W21" s="6"/>
+      <c r="X21" s="6"/>
+      <c r="Y21" s="6"/>
+      <c r="Z21" s="6"/>
+      <c r="AA21" s="6"/>
+      <c r="AB21" s="6"/>
+      <c r="AC21" s="6"/>
+      <c r="AD21" s="6"/>
+      <c r="AE21" s="6"/>
+      <c r="AF21" s="6"/>
+      <c r="AG21" s="6"/>
+      <c r="AH21" s="6"/>
+      <c r="AI21" s="6"/>
+      <c r="AJ21" s="6"/>
+      <c r="AK21" s="6"/>
+      <c r="AL21" s="6"/>
+      <c r="AM21" s="6"/>
+      <c r="AN21" s="6"/>
+      <c r="AO21" s="6"/>
+      <c r="AP21" s="6"/>
+      <c r="AQ21" s="6"/>
+      <c r="AR21" s="6"/>
+      <c r="AS21" s="6"/>
+      <c r="AT21" s="6"/>
+      <c r="AU21" s="6"/>
+      <c r="AV21" s="6"/>
+      <c r="AW21" s="56"/>
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A22" s="89"/>
-      <c r="B22" s="89"/>
-      <c r="C22" s="89"/>
-      <c r="D22" s="89"/>
-      <c r="E22" s="89"/>
-      <c r="F22" s="89"/>
-      <c r="G22" s="89"/>
-      <c r="H22" s="90"/>
-      <c r="I22" s="90"/>
-      <c r="J22" s="90"/>
-      <c r="K22" s="90"/>
-      <c r="L22" s="90"/>
-      <c r="M22" s="90"/>
-      <c r="N22" s="89"/>
-      <c r="O22" s="89"/>
-      <c r="P22" s="89"/>
-      <c r="Q22" s="89"/>
-      <c r="R22" s="89"/>
-      <c r="S22" s="89"/>
-      <c r="T22" s="89"/>
-      <c r="U22" s="89"/>
-      <c r="V22" s="89"/>
-      <c r="W22" s="89"/>
-      <c r="X22" s="89"/>
-      <c r="Y22" s="89"/>
-      <c r="Z22" s="89"/>
-      <c r="AA22" s="89"/>
-      <c r="AB22" s="89"/>
-      <c r="AC22" s="89"/>
-      <c r="AD22" s="89"/>
-      <c r="AE22" s="89"/>
-      <c r="AF22" s="89"/>
-      <c r="AG22" s="89"/>
-      <c r="AH22" s="89"/>
-      <c r="AI22" s="89"/>
-      <c r="AJ22" s="89"/>
-      <c r="AK22" s="89"/>
-      <c r="AL22" s="89"/>
-      <c r="AM22" s="89"/>
-      <c r="AN22" s="89"/>
-      <c r="AO22" s="89"/>
-      <c r="AP22" s="89"/>
-      <c r="AQ22" s="89"/>
-      <c r="AR22" s="89"/>
-      <c r="AS22" s="89"/>
-      <c r="AT22" s="89"/>
-      <c r="AU22" s="89"/>
-      <c r="AV22" s="89"/>
-      <c r="AW22" s="87"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="62"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="6"/>
+      <c r="T22" s="6"/>
+      <c r="U22" s="6"/>
+      <c r="V22" s="6"/>
+      <c r="W22" s="6"/>
+      <c r="X22" s="6"/>
+      <c r="Y22" s="6"/>
+      <c r="Z22" s="6"/>
+      <c r="AA22" s="6"/>
+      <c r="AB22" s="6"/>
+      <c r="AC22" s="6"/>
+      <c r="AD22" s="6"/>
+      <c r="AE22" s="6"/>
+      <c r="AF22" s="6"/>
+      <c r="AG22" s="6"/>
+      <c r="AH22" s="6"/>
+      <c r="AI22" s="6"/>
+      <c r="AJ22" s="6"/>
+      <c r="AK22" s="6"/>
+      <c r="AL22" s="6"/>
+      <c r="AM22" s="6"/>
+      <c r="AN22" s="6"/>
+      <c r="AO22" s="6"/>
+      <c r="AP22" s="6"/>
+      <c r="AQ22" s="6"/>
+      <c r="AR22" s="6"/>
+      <c r="AS22" s="6"/>
+      <c r="AT22" s="6"/>
+      <c r="AU22" s="6"/>
+      <c r="AV22" s="6"/>
+      <c r="AW22" s="56"/>
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A23" s="89"/>
-      <c r="B23" s="89"/>
-      <c r="C23" s="89"/>
-      <c r="D23" s="89"/>
-      <c r="E23" s="89"/>
-      <c r="F23" s="89"/>
-      <c r="G23" s="89"/>
-      <c r="H23" s="89"/>
-      <c r="I23" s="89"/>
-      <c r="J23" s="89"/>
-      <c r="K23" s="89"/>
-      <c r="L23" s="89"/>
-      <c r="M23" s="89"/>
-      <c r="N23" s="89"/>
-      <c r="O23" s="89"/>
-      <c r="P23" s="89"/>
-      <c r="Q23" s="89"/>
-      <c r="R23" s="89"/>
-      <c r="S23" s="89"/>
-      <c r="T23" s="89"/>
-      <c r="U23" s="89"/>
-      <c r="V23" s="89"/>
-      <c r="W23" s="89"/>
-      <c r="X23" s="89"/>
-      <c r="Y23" s="89"/>
-      <c r="Z23" s="89"/>
-      <c r="AA23" s="89"/>
-      <c r="AB23" s="89"/>
-      <c r="AC23" s="89"/>
-      <c r="AD23" s="89"/>
-      <c r="AE23" s="89"/>
-      <c r="AF23" s="89"/>
-      <c r="AG23" s="89"/>
-      <c r="AH23" s="89"/>
-      <c r="AI23" s="89"/>
-      <c r="AJ23" s="89"/>
-      <c r="AK23" s="89"/>
-      <c r="AL23" s="89"/>
-      <c r="AM23" s="89"/>
-      <c r="AN23" s="89"/>
-      <c r="AO23" s="89"/>
-      <c r="AP23" s="89"/>
-      <c r="AQ23" s="89"/>
-      <c r="AR23" s="89"/>
-      <c r="AS23" s="89"/>
-      <c r="AT23" s="89"/>
-      <c r="AU23" s="89"/>
-      <c r="AV23" s="89"/>
-      <c r="AW23" s="87"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="6"/>
+      <c r="S23" s="6"/>
+      <c r="T23" s="6"/>
+      <c r="U23" s="6"/>
+      <c r="V23" s="6"/>
+      <c r="W23" s="6"/>
+      <c r="X23" s="6"/>
+      <c r="Y23" s="6"/>
+      <c r="Z23" s="6"/>
+      <c r="AA23" s="6"/>
+      <c r="AB23" s="6"/>
+      <c r="AC23" s="6"/>
+      <c r="AD23" s="6"/>
+      <c r="AE23" s="6"/>
+      <c r="AF23" s="6"/>
+      <c r="AG23" s="6"/>
+      <c r="AH23" s="6"/>
+      <c r="AI23" s="6"/>
+      <c r="AJ23" s="6"/>
+      <c r="AK23" s="6"/>
+      <c r="AL23" s="6"/>
+      <c r="AM23" s="6"/>
+      <c r="AN23" s="6"/>
+      <c r="AO23" s="6"/>
+      <c r="AP23" s="6"/>
+      <c r="AQ23" s="6"/>
+      <c r="AR23" s="6"/>
+      <c r="AS23" s="6"/>
+      <c r="AT23" s="6"/>
+      <c r="AU23" s="6"/>
+      <c r="AV23" s="6"/>
+      <c r="AW23" s="56"/>
     </row>
     <row r="24" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A24" s="89"/>
-      <c r="B24" s="89"/>
-      <c r="C24" s="89"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="89"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="89"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="89"/>
-      <c r="J24" s="89"/>
-      <c r="K24" s="89"/>
-      <c r="L24" s="89"/>
-      <c r="M24" s="89"/>
-      <c r="N24" s="89"/>
-      <c r="O24" s="89"/>
-      <c r="P24" s="89"/>
-      <c r="Q24" s="89"/>
-      <c r="R24" s="89"/>
-      <c r="S24" s="89"/>
-      <c r="T24" s="89"/>
-      <c r="U24" s="89"/>
-      <c r="V24" s="89"/>
-      <c r="W24" s="89"/>
-      <c r="X24" s="89"/>
-      <c r="Y24" s="89"/>
-      <c r="Z24" s="89"/>
-      <c r="AA24" s="89"/>
-      <c r="AB24" s="89"/>
-      <c r="AC24" s="89"/>
-      <c r="AD24" s="89"/>
-      <c r="AE24" s="89"/>
-      <c r="AF24" s="89"/>
-      <c r="AG24" s="89"/>
-      <c r="AH24" s="89"/>
-      <c r="AI24" s="89"/>
-      <c r="AJ24" s="89"/>
-      <c r="AK24" s="89"/>
-      <c r="AL24" s="89"/>
-      <c r="AM24" s="89"/>
-      <c r="AN24" s="89"/>
-      <c r="AO24" s="89"/>
-      <c r="AP24" s="89"/>
-      <c r="AQ24" s="89"/>
-      <c r="AR24" s="89"/>
-      <c r="AS24" s="89"/>
-      <c r="AT24" s="89"/>
-      <c r="AU24" s="89"/>
-      <c r="AV24" s="89"/>
-      <c r="AW24" s="87"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="6"/>
+      <c r="S24" s="6"/>
+      <c r="T24" s="6"/>
+      <c r="U24" s="6"/>
+      <c r="V24" s="6"/>
+      <c r="W24" s="6"/>
+      <c r="X24" s="6"/>
+      <c r="Y24" s="6"/>
+      <c r="Z24" s="6"/>
+      <c r="AA24" s="6"/>
+      <c r="AB24" s="6"/>
+      <c r="AC24" s="6"/>
+      <c r="AD24" s="6"/>
+      <c r="AE24" s="6"/>
+      <c r="AF24" s="6"/>
+      <c r="AG24" s="6"/>
+      <c r="AH24" s="6"/>
+      <c r="AI24" s="6"/>
+      <c r="AJ24" s="6"/>
+      <c r="AK24" s="6"/>
+      <c r="AL24" s="6"/>
+      <c r="AM24" s="6"/>
+      <c r="AN24" s="6"/>
+      <c r="AO24" s="6"/>
+      <c r="AP24" s="6"/>
+      <c r="AQ24" s="6"/>
+      <c r="AR24" s="6"/>
+      <c r="AS24" s="6"/>
+      <c r="AT24" s="6"/>
+      <c r="AU24" s="6"/>
+      <c r="AV24" s="6"/>
+      <c r="AW24" s="56"/>
     </row>
     <row r="25" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A25" s="89"/>
-      <c r="B25" s="89"/>
-      <c r="C25" s="89"/>
-      <c r="D25" s="89"/>
-      <c r="E25" s="89"/>
-      <c r="F25" s="89"/>
-      <c r="G25" s="89"/>
-      <c r="H25" s="89"/>
-      <c r="I25" s="89"/>
-      <c r="J25" s="89"/>
-      <c r="K25" s="89"/>
-      <c r="L25" s="89"/>
-      <c r="M25" s="89"/>
-      <c r="N25" s="89"/>
-      <c r="O25" s="89"/>
-      <c r="P25" s="89"/>
-      <c r="Q25" s="89"/>
-      <c r="R25" s="89"/>
-      <c r="S25" s="89"/>
-      <c r="T25" s="89"/>
-      <c r="U25" s="89"/>
-      <c r="V25" s="89"/>
-      <c r="W25" s="89"/>
-      <c r="X25" s="89"/>
-      <c r="Y25" s="89"/>
-      <c r="Z25" s="89"/>
-      <c r="AA25" s="89"/>
-      <c r="AB25" s="89"/>
-      <c r="AC25" s="89"/>
-      <c r="AD25" s="89"/>
-      <c r="AE25" s="89"/>
-      <c r="AF25" s="89"/>
-      <c r="AG25" s="89"/>
-      <c r="AH25" s="89"/>
-      <c r="AI25" s="89"/>
-      <c r="AJ25" s="89"/>
-      <c r="AK25" s="89"/>
-      <c r="AL25" s="89"/>
-      <c r="AM25" s="89"/>
-      <c r="AN25" s="89"/>
-      <c r="AO25" s="89"/>
-      <c r="AP25" s="89"/>
-      <c r="AQ25" s="89"/>
-      <c r="AR25" s="89"/>
-      <c r="AS25" s="89"/>
-      <c r="AT25" s="89"/>
-      <c r="AU25" s="89"/>
-      <c r="AV25" s="89"/>
-      <c r="AW25" s="87"/>
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
+      <c r="R25" s="6"/>
+      <c r="S25" s="6"/>
+      <c r="T25" s="6"/>
+      <c r="U25" s="6"/>
+      <c r="V25" s="6"/>
+      <c r="W25" s="6"/>
+      <c r="X25" s="6"/>
+      <c r="Y25" s="6"/>
+      <c r="Z25" s="6"/>
+      <c r="AA25" s="6"/>
+      <c r="AB25" s="6"/>
+      <c r="AC25" s="6"/>
+      <c r="AD25" s="6"/>
+      <c r="AE25" s="6"/>
+      <c r="AF25" s="6"/>
+      <c r="AG25" s="6"/>
+      <c r="AH25" s="6"/>
+      <c r="AI25" s="6"/>
+      <c r="AJ25" s="6"/>
+      <c r="AK25" s="6"/>
+      <c r="AL25" s="6"/>
+      <c r="AM25" s="6"/>
+      <c r="AN25" s="6"/>
+      <c r="AO25" s="6"/>
+      <c r="AP25" s="6"/>
+      <c r="AQ25" s="6"/>
+      <c r="AR25" s="6"/>
+      <c r="AS25" s="6"/>
+      <c r="AT25" s="6"/>
+      <c r="AU25" s="6"/>
+      <c r="AV25" s="6"/>
+      <c r="AW25" s="56"/>
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A26" s="89"/>
-      <c r="B26" s="89"/>
-      <c r="C26" s="89"/>
-      <c r="D26" s="89"/>
-      <c r="E26" s="89"/>
-      <c r="F26" s="89"/>
-      <c r="G26" s="89"/>
-      <c r="H26" s="89"/>
-      <c r="I26" s="89"/>
-      <c r="J26" s="89"/>
-      <c r="K26" s="89"/>
-      <c r="L26" s="89"/>
-      <c r="M26" s="89"/>
-      <c r="N26" s="89"/>
-      <c r="O26" s="89"/>
-      <c r="P26" s="89"/>
-      <c r="Q26" s="89"/>
-      <c r="R26" s="89"/>
-      <c r="S26" s="89"/>
-      <c r="T26" s="89"/>
-      <c r="U26" s="89"/>
-      <c r="V26" s="89"/>
-      <c r="W26" s="89"/>
-      <c r="X26" s="89"/>
-      <c r="Y26" s="89"/>
-      <c r="Z26" s="89"/>
-      <c r="AA26" s="89"/>
-      <c r="AB26" s="89"/>
-      <c r="AC26" s="89"/>
-      <c r="AD26" s="89"/>
-      <c r="AE26" s="89"/>
-      <c r="AF26" s="89"/>
-      <c r="AG26" s="89"/>
-      <c r="AH26" s="89"/>
-      <c r="AI26" s="89"/>
-      <c r="AJ26" s="89"/>
-      <c r="AK26" s="89"/>
-      <c r="AL26" s="89"/>
-      <c r="AM26" s="89"/>
-      <c r="AN26" s="89"/>
-      <c r="AO26" s="89"/>
-      <c r="AP26" s="89"/>
-      <c r="AQ26" s="89"/>
-      <c r="AR26" s="89"/>
-      <c r="AS26" s="89"/>
-      <c r="AT26" s="89"/>
-      <c r="AU26" s="89"/>
-      <c r="AV26" s="89"/>
-      <c r="AW26" s="87"/>
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="6"/>
+      <c r="R26" s="6"/>
+      <c r="S26" s="6"/>
+      <c r="T26" s="6"/>
+      <c r="U26" s="6"/>
+      <c r="V26" s="6"/>
+      <c r="W26" s="6"/>
+      <c r="X26" s="6"/>
+      <c r="Y26" s="6"/>
+      <c r="Z26" s="6"/>
+      <c r="AA26" s="6"/>
+      <c r="AB26" s="6"/>
+      <c r="AC26" s="6"/>
+      <c r="AD26" s="6"/>
+      <c r="AE26" s="6"/>
+      <c r="AF26" s="6"/>
+      <c r="AG26" s="6"/>
+      <c r="AH26" s="6"/>
+      <c r="AI26" s="6"/>
+      <c r="AJ26" s="6"/>
+      <c r="AK26" s="6"/>
+      <c r="AL26" s="6"/>
+      <c r="AM26" s="6"/>
+      <c r="AN26" s="6"/>
+      <c r="AO26" s="6"/>
+      <c r="AP26" s="6"/>
+      <c r="AQ26" s="6"/>
+      <c r="AR26" s="6"/>
+      <c r="AS26" s="6"/>
+      <c r="AT26" s="6"/>
+      <c r="AU26" s="6"/>
+      <c r="AV26" s="6"/>
+      <c r="AW26" s="56"/>
     </row>
     <row r="27" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A27" s="89"/>
-      <c r="B27" s="89"/>
-      <c r="C27" s="89"/>
-      <c r="D27" s="89"/>
-      <c r="E27" s="89"/>
-      <c r="F27" s="89"/>
-      <c r="G27" s="89"/>
-      <c r="H27" s="89"/>
-      <c r="I27" s="89"/>
-      <c r="J27" s="89"/>
-      <c r="K27" s="89"/>
-      <c r="L27" s="89"/>
-      <c r="M27" s="89"/>
-      <c r="N27" s="89"/>
-      <c r="O27" s="89"/>
-      <c r="P27" s="89"/>
-      <c r="Q27" s="89"/>
-      <c r="R27" s="89"/>
-      <c r="S27" s="89"/>
-      <c r="T27" s="89"/>
-      <c r="U27" s="89"/>
-      <c r="V27" s="89"/>
-      <c r="W27" s="89"/>
-      <c r="X27" s="89"/>
-      <c r="Y27" s="89"/>
-      <c r="Z27" s="89"/>
-      <c r="AA27" s="89"/>
-      <c r="AB27" s="89"/>
-      <c r="AC27" s="89"/>
-      <c r="AD27" s="89"/>
-      <c r="AE27" s="89"/>
-      <c r="AF27" s="89"/>
-      <c r="AG27" s="89"/>
-      <c r="AH27" s="89"/>
-      <c r="AI27" s="89"/>
-      <c r="AJ27" s="89"/>
-      <c r="AK27" s="89"/>
-      <c r="AL27" s="89"/>
-      <c r="AM27" s="89"/>
-      <c r="AN27" s="89"/>
-      <c r="AO27" s="89"/>
-      <c r="AP27" s="89"/>
-      <c r="AQ27" s="89"/>
-      <c r="AR27" s="89"/>
-      <c r="AS27" s="89"/>
-      <c r="AT27" s="89"/>
-      <c r="AU27" s="89"/>
-      <c r="AV27" s="89"/>
-      <c r="AW27" s="87"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+      <c r="P27" s="6"/>
+      <c r="Q27" s="6"/>
+      <c r="R27" s="6"/>
+      <c r="S27" s="6"/>
+      <c r="T27" s="6"/>
+      <c r="U27" s="6"/>
+      <c r="V27" s="6"/>
+      <c r="W27" s="6"/>
+      <c r="X27" s="6"/>
+      <c r="Y27" s="6"/>
+      <c r="Z27" s="6"/>
+      <c r="AA27" s="6"/>
+      <c r="AB27" s="6"/>
+      <c r="AC27" s="6"/>
+      <c r="AD27" s="6"/>
+      <c r="AE27" s="6"/>
+      <c r="AF27" s="6"/>
+      <c r="AG27" s="6"/>
+      <c r="AH27" s="6"/>
+      <c r="AI27" s="6"/>
+      <c r="AJ27" s="6"/>
+      <c r="AK27" s="6"/>
+      <c r="AL27" s="6"/>
+      <c r="AM27" s="6"/>
+      <c r="AN27" s="6"/>
+      <c r="AO27" s="6"/>
+      <c r="AP27" s="6"/>
+      <c r="AQ27" s="6"/>
+      <c r="AR27" s="6"/>
+      <c r="AS27" s="6"/>
+      <c r="AT27" s="6"/>
+      <c r="AU27" s="6"/>
+      <c r="AV27" s="6"/>
+      <c r="AW27" s="56"/>
     </row>
     <row r="28" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A28" s="89"/>
-      <c r="B28" s="89"/>
-      <c r="C28" s="89"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="89"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="89"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="89"/>
-      <c r="K28" s="89"/>
-      <c r="L28" s="89"/>
-      <c r="M28" s="89"/>
-      <c r="N28" s="89"/>
-      <c r="O28" s="89"/>
-      <c r="P28" s="89"/>
-      <c r="Q28" s="89"/>
-      <c r="R28" s="89"/>
-      <c r="S28" s="89"/>
-      <c r="T28" s="89"/>
-      <c r="U28" s="89"/>
-      <c r="V28" s="89"/>
-      <c r="W28" s="89"/>
-      <c r="X28" s="89"/>
-      <c r="Y28" s="89"/>
-      <c r="Z28" s="89"/>
-      <c r="AA28" s="89"/>
-      <c r="AB28" s="89"/>
-      <c r="AC28" s="89"/>
-      <c r="AD28" s="89"/>
-      <c r="AE28" s="89"/>
-      <c r="AF28" s="89"/>
-      <c r="AG28" s="89"/>
-      <c r="AH28" s="89"/>
-      <c r="AI28" s="89"/>
-      <c r="AJ28" s="89"/>
-      <c r="AK28" s="89"/>
-      <c r="AL28" s="89"/>
-      <c r="AM28" s="89"/>
-      <c r="AN28" s="89"/>
-      <c r="AO28" s="89"/>
-      <c r="AP28" s="89"/>
-      <c r="AQ28" s="89"/>
-      <c r="AR28" s="89"/>
-      <c r="AS28" s="89"/>
-      <c r="AT28" s="89"/>
-      <c r="AU28" s="89"/>
-      <c r="AV28" s="89"/>
-      <c r="AW28" s="87"/>
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
+      <c r="P28" s="6"/>
+      <c r="Q28" s="6"/>
+      <c r="R28" s="6"/>
+      <c r="S28" s="6"/>
+      <c r="T28" s="6"/>
+      <c r="U28" s="6"/>
+      <c r="V28" s="6"/>
+      <c r="W28" s="6"/>
+      <c r="X28" s="6"/>
+      <c r="Y28" s="6"/>
+      <c r="Z28" s="6"/>
+      <c r="AA28" s="6"/>
+      <c r="AB28" s="6"/>
+      <c r="AC28" s="6"/>
+      <c r="AD28" s="6"/>
+      <c r="AE28" s="6"/>
+      <c r="AF28" s="6"/>
+      <c r="AG28" s="6"/>
+      <c r="AH28" s="6"/>
+      <c r="AI28" s="6"/>
+      <c r="AJ28" s="6"/>
+      <c r="AK28" s="6"/>
+      <c r="AL28" s="6"/>
+      <c r="AM28" s="6"/>
+      <c r="AN28" s="6"/>
+      <c r="AO28" s="6"/>
+      <c r="AP28" s="6"/>
+      <c r="AQ28" s="6"/>
+      <c r="AR28" s="6"/>
+      <c r="AS28" s="6"/>
+      <c r="AT28" s="6"/>
+      <c r="AU28" s="6"/>
+      <c r="AV28" s="6"/>
+      <c r="AW28" s="56"/>
     </row>
     <row r="29" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A29" s="89"/>
-      <c r="B29" s="89"/>
-      <c r="C29" s="89"/>
-      <c r="D29" s="89"/>
-      <c r="E29" s="89"/>
-      <c r="F29" s="89"/>
-      <c r="G29" s="89"/>
-      <c r="H29" s="89"/>
-      <c r="I29" s="89"/>
-      <c r="J29" s="89"/>
-      <c r="K29" s="89"/>
-      <c r="L29" s="89"/>
-      <c r="M29" s="89"/>
-      <c r="N29" s="89"/>
-      <c r="O29" s="89"/>
-      <c r="P29" s="89"/>
-      <c r="Q29" s="89"/>
-      <c r="R29" s="89"/>
-      <c r="S29" s="89"/>
-      <c r="T29" s="89"/>
-      <c r="U29" s="89"/>
-      <c r="V29" s="89"/>
-      <c r="W29" s="89"/>
-      <c r="X29" s="89"/>
-      <c r="Y29" s="89"/>
-      <c r="Z29" s="89"/>
-      <c r="AA29" s="89"/>
-      <c r="AB29" s="89"/>
-      <c r="AC29" s="89"/>
-      <c r="AD29" s="89"/>
-      <c r="AE29" s="89"/>
-      <c r="AF29" s="89"/>
-      <c r="AG29" s="89"/>
-      <c r="AH29" s="89"/>
-      <c r="AI29" s="89"/>
-      <c r="AJ29" s="89"/>
-      <c r="AK29" s="89"/>
-      <c r="AL29" s="89"/>
-      <c r="AM29" s="89"/>
-      <c r="AN29" s="89"/>
-      <c r="AO29" s="89"/>
-      <c r="AP29" s="89"/>
-      <c r="AQ29" s="89"/>
-      <c r="AR29" s="89"/>
-      <c r="AS29" s="89"/>
-      <c r="AT29" s="89"/>
-      <c r="AU29" s="89"/>
-      <c r="AV29" s="89"/>
-      <c r="AW29" s="87"/>
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
+      <c r="P29" s="6"/>
+      <c r="Q29" s="6"/>
+      <c r="R29" s="6"/>
+      <c r="S29" s="6"/>
+      <c r="T29" s="6"/>
+      <c r="U29" s="6"/>
+      <c r="V29" s="6"/>
+      <c r="W29" s="6"/>
+      <c r="X29" s="6"/>
+      <c r="Y29" s="6"/>
+      <c r="Z29" s="6"/>
+      <c r="AA29" s="6"/>
+      <c r="AB29" s="6"/>
+      <c r="AC29" s="6"/>
+      <c r="AD29" s="6"/>
+      <c r="AE29" s="6"/>
+      <c r="AF29" s="6"/>
+      <c r="AG29" s="6"/>
+      <c r="AH29" s="6"/>
+      <c r="AI29" s="6"/>
+      <c r="AJ29" s="6"/>
+      <c r="AK29" s="6"/>
+      <c r="AL29" s="6"/>
+      <c r="AM29" s="6"/>
+      <c r="AN29" s="6"/>
+      <c r="AO29" s="6"/>
+      <c r="AP29" s="6"/>
+      <c r="AQ29" s="6"/>
+      <c r="AR29" s="6"/>
+      <c r="AS29" s="6"/>
+      <c r="AT29" s="6"/>
+      <c r="AU29" s="6"/>
+      <c r="AV29" s="6"/>
+      <c r="AW29" s="56"/>
     </row>
     <row r="30" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A30" s="89"/>
-      <c r="B30" s="89"/>
-      <c r="C30" s="89"/>
-      <c r="D30" s="89"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="89"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="89"/>
-      <c r="K30" s="89"/>
-      <c r="L30" s="89"/>
-      <c r="M30" s="89"/>
-      <c r="N30" s="89"/>
-      <c r="O30" s="89"/>
-      <c r="P30" s="89"/>
-      <c r="Q30" s="89"/>
-      <c r="R30" s="89"/>
-      <c r="S30" s="89"/>
-      <c r="T30" s="89"/>
-      <c r="U30" s="89"/>
-      <c r="V30" s="89"/>
-      <c r="W30" s="89"/>
-      <c r="X30" s="89"/>
-      <c r="Y30" s="89"/>
-      <c r="Z30" s="89"/>
-      <c r="AA30" s="89"/>
-      <c r="AB30" s="89"/>
-      <c r="AC30" s="89"/>
-      <c r="AD30" s="89"/>
-      <c r="AE30" s="89"/>
-      <c r="AF30" s="89"/>
-      <c r="AG30" s="89"/>
-      <c r="AH30" s="89"/>
-      <c r="AI30" s="89"/>
-      <c r="AJ30" s="89"/>
-      <c r="AK30" s="89"/>
-      <c r="AL30" s="89"/>
-      <c r="AM30" s="89"/>
-      <c r="AN30" s="89"/>
-      <c r="AO30" s="89"/>
-      <c r="AP30" s="89"/>
-      <c r="AQ30" s="89"/>
-      <c r="AR30" s="89"/>
-      <c r="AS30" s="89"/>
-      <c r="AT30" s="89"/>
-      <c r="AU30" s="89"/>
-      <c r="AV30" s="89"/>
-      <c r="AW30" s="87"/>
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
+      <c r="P30" s="6"/>
+      <c r="Q30" s="6"/>
+      <c r="R30" s="6"/>
+      <c r="S30" s="6"/>
+      <c r="T30" s="6"/>
+      <c r="U30" s="6"/>
+      <c r="V30" s="6"/>
+      <c r="W30" s="6"/>
+      <c r="X30" s="6"/>
+      <c r="Y30" s="6"/>
+      <c r="Z30" s="6"/>
+      <c r="AA30" s="6"/>
+      <c r="AB30" s="6"/>
+      <c r="AC30" s="6"/>
+      <c r="AD30" s="6"/>
+      <c r="AE30" s="6"/>
+      <c r="AF30" s="6"/>
+      <c r="AG30" s="6"/>
+      <c r="AH30" s="6"/>
+      <c r="AI30" s="6"/>
+      <c r="AJ30" s="6"/>
+      <c r="AK30" s="6"/>
+      <c r="AL30" s="6"/>
+      <c r="AM30" s="6"/>
+      <c r="AN30" s="6"/>
+      <c r="AO30" s="6"/>
+      <c r="AP30" s="6"/>
+      <c r="AQ30" s="6"/>
+      <c r="AR30" s="6"/>
+      <c r="AS30" s="6"/>
+      <c r="AT30" s="6"/>
+      <c r="AU30" s="6"/>
+      <c r="AV30" s="6"/>
+      <c r="AW30" s="56"/>
     </row>
     <row r="31" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A31" s="89"/>
-      <c r="B31" s="89"/>
-      <c r="C31" s="89"/>
-      <c r="D31" s="89"/>
-      <c r="E31" s="89"/>
-      <c r="F31" s="89"/>
-      <c r="G31" s="89"/>
-      <c r="H31" s="89"/>
-      <c r="I31" s="89"/>
-      <c r="J31" s="89"/>
-      <c r="K31" s="89"/>
-      <c r="L31" s="89"/>
-      <c r="M31" s="89"/>
-      <c r="N31" s="89"/>
-      <c r="O31" s="89"/>
-      <c r="P31" s="89"/>
-      <c r="Q31" s="89"/>
-      <c r="R31" s="89"/>
-      <c r="S31" s="89"/>
-      <c r="T31" s="89"/>
-      <c r="U31" s="89"/>
-      <c r="V31" s="89"/>
-      <c r="W31" s="89"/>
-      <c r="X31" s="89"/>
-      <c r="Y31" s="89"/>
-      <c r="Z31" s="89"/>
-      <c r="AA31" s="89"/>
-      <c r="AB31" s="89"/>
-      <c r="AC31" s="89"/>
-      <c r="AD31" s="89"/>
-      <c r="AE31" s="89"/>
-      <c r="AF31" s="89"/>
-      <c r="AG31" s="89"/>
-      <c r="AH31" s="89"/>
-      <c r="AI31" s="89"/>
-      <c r="AJ31" s="89"/>
-      <c r="AK31" s="89"/>
-      <c r="AL31" s="89"/>
-      <c r="AM31" s="89"/>
-      <c r="AN31" s="89"/>
-      <c r="AO31" s="89"/>
-      <c r="AP31" s="89"/>
-      <c r="AQ31" s="89"/>
-      <c r="AR31" s="89"/>
-      <c r="AS31" s="89"/>
-      <c r="AT31" s="89"/>
-      <c r="AU31" s="89"/>
-      <c r="AV31" s="89"/>
-      <c r="AW31" s="87"/>
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="6"/>
+      <c r="Q31" s="6"/>
+      <c r="R31" s="6"/>
+      <c r="S31" s="6"/>
+      <c r="T31" s="6"/>
+      <c r="U31" s="6"/>
+      <c r="V31" s="6"/>
+      <c r="W31" s="6"/>
+      <c r="X31" s="6"/>
+      <c r="Y31" s="6"/>
+      <c r="Z31" s="6"/>
+      <c r="AA31" s="6"/>
+      <c r="AB31" s="6"/>
+      <c r="AC31" s="6"/>
+      <c r="AD31" s="6"/>
+      <c r="AE31" s="6"/>
+      <c r="AF31" s="6"/>
+      <c r="AG31" s="6"/>
+      <c r="AH31" s="6"/>
+      <c r="AI31" s="6"/>
+      <c r="AJ31" s="6"/>
+      <c r="AK31" s="6"/>
+      <c r="AL31" s="6"/>
+      <c r="AM31" s="6"/>
+      <c r="AN31" s="6"/>
+      <c r="AO31" s="6"/>
+      <c r="AP31" s="6"/>
+      <c r="AQ31" s="6"/>
+      <c r="AR31" s="6"/>
+      <c r="AS31" s="6"/>
+      <c r="AT31" s="6"/>
+      <c r="AU31" s="6"/>
+      <c r="AV31" s="6"/>
+      <c r="AW31" s="56"/>
     </row>
     <row r="32" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A32" s="89"/>
-      <c r="B32" s="89"/>
-      <c r="C32" s="89"/>
-      <c r="D32" s="89"/>
-      <c r="E32" s="89"/>
-      <c r="F32" s="89"/>
-      <c r="G32" s="89"/>
-      <c r="H32" s="89"/>
-      <c r="I32" s="89"/>
-      <c r="J32" s="89"/>
-      <c r="K32" s="89"/>
-      <c r="L32" s="89"/>
-      <c r="M32" s="89"/>
-      <c r="N32" s="89"/>
-      <c r="O32" s="89"/>
-      <c r="P32" s="89"/>
-      <c r="Q32" s="89"/>
-      <c r="R32" s="89"/>
-      <c r="S32" s="89"/>
-      <c r="T32" s="89"/>
-      <c r="U32" s="89"/>
-      <c r="V32" s="89"/>
-      <c r="W32" s="89"/>
-      <c r="X32" s="89"/>
-      <c r="Y32" s="89"/>
-      <c r="Z32" s="89"/>
-      <c r="AA32" s="89"/>
-      <c r="AB32" s="89"/>
-      <c r="AC32" s="89"/>
-      <c r="AD32" s="89"/>
-      <c r="AE32" s="89"/>
-      <c r="AF32" s="89"/>
-      <c r="AG32" s="89"/>
-      <c r="AH32" s="89"/>
-      <c r="AI32" s="89"/>
-      <c r="AJ32" s="89"/>
-      <c r="AK32" s="89"/>
-      <c r="AL32" s="89"/>
-      <c r="AM32" s="89"/>
-      <c r="AN32" s="89"/>
-      <c r="AO32" s="89"/>
-      <c r="AP32" s="89"/>
-      <c r="AQ32" s="89"/>
-      <c r="AR32" s="89"/>
-      <c r="AS32" s="89"/>
-      <c r="AT32" s="89"/>
-      <c r="AU32" s="89"/>
-      <c r="AV32" s="89"/>
-      <c r="AW32" s="87"/>
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
+      <c r="P32" s="6"/>
+      <c r="Q32" s="6"/>
+      <c r="R32" s="6"/>
+      <c r="S32" s="6"/>
+      <c r="T32" s="6"/>
+      <c r="U32" s="6"/>
+      <c r="V32" s="6"/>
+      <c r="W32" s="6"/>
+      <c r="X32" s="6"/>
+      <c r="Y32" s="6"/>
+      <c r="Z32" s="6"/>
+      <c r="AA32" s="6"/>
+      <c r="AB32" s="6"/>
+      <c r="AC32" s="6"/>
+      <c r="AD32" s="6"/>
+      <c r="AE32" s="6"/>
+      <c r="AF32" s="6"/>
+      <c r="AG32" s="6"/>
+      <c r="AH32" s="6"/>
+      <c r="AI32" s="6"/>
+      <c r="AJ32" s="6"/>
+      <c r="AK32" s="6"/>
+      <c r="AL32" s="6"/>
+      <c r="AM32" s="6"/>
+      <c r="AN32" s="6"/>
+      <c r="AO32" s="6"/>
+      <c r="AP32" s="6"/>
+      <c r="AQ32" s="6"/>
+      <c r="AR32" s="6"/>
+      <c r="AS32" s="6"/>
+      <c r="AT32" s="6"/>
+      <c r="AU32" s="6"/>
+      <c r="AV32" s="6"/>
+      <c r="AW32" s="56"/>
     </row>
     <row r="33" spans="29:48" x14ac:dyDescent="0.3">
       <c r="AC33" s="53"/>
@@ -10725,49 +10719,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="57" t="s">
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="60" t="s">
         <v>140</v>
       </c>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="58"/>
-      <c r="S1" s="58"/>
-      <c r="T1" s="58"/>
-      <c r="U1" s="58"/>
-      <c r="V1" s="58"/>
-      <c r="W1" s="58"/>
-      <c r="X1" s="58"/>
-      <c r="Y1" s="58"/>
-      <c r="Z1" s="58"/>
-      <c r="AA1" s="58"/>
-      <c r="AB1" s="58"/>
-      <c r="AC1" s="58"/>
-      <c r="AD1" s="58"/>
-      <c r="AE1" s="58"/>
-      <c r="AF1" s="58"/>
-      <c r="AG1" s="58"/>
-      <c r="AH1" s="58"/>
-      <c r="AI1" s="58"/>
-      <c r="AJ1" s="58"/>
-      <c r="AK1" s="58"/>
-      <c r="AL1" s="58"/>
-      <c r="AM1" s="58"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="61"/>
+      <c r="P1" s="61"/>
+      <c r="Q1" s="61"/>
+      <c r="R1" s="61"/>
+      <c r="S1" s="61"/>
+      <c r="T1" s="61"/>
+      <c r="U1" s="61"/>
+      <c r="V1" s="61"/>
+      <c r="W1" s="61"/>
+      <c r="X1" s="61"/>
+      <c r="Y1" s="61"/>
+      <c r="Z1" s="61"/>
+      <c r="AA1" s="61"/>
+      <c r="AB1" s="61"/>
+      <c r="AC1" s="61"/>
+      <c r="AD1" s="61"/>
+      <c r="AE1" s="61"/>
+      <c r="AF1" s="61"/>
+      <c r="AG1" s="61"/>
+      <c r="AH1" s="61"/>
+      <c r="AI1" s="61"/>
+      <c r="AJ1" s="61"/>
+      <c r="AK1" s="61"/>
+      <c r="AL1" s="61"/>
+      <c r="AM1" s="61"/>
     </row>
     <row r="2" spans="1:39" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -10782,11 +10776,11 @@
       <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="75" t="s">
+      <c r="E2" s="79" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="76"/>
-      <c r="G2" s="77"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="81"/>
       <c r="H2" s="39" t="s">
         <v>105</v>
       </c>
@@ -10897,11 +10891,11 @@
       <c r="D3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="60" t="s">
+      <c r="E3" s="63" t="s">
         <v>247</v>
       </c>
-      <c r="F3" s="61"/>
-      <c r="G3" s="62"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="65"/>
       <c r="H3" s="13">
         <v>4</v>
       </c>
@@ -10974,11 +10968,11 @@
       <c r="D4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="84" t="s">
+      <c r="E4" s="82" t="s">
         <v>248</v>
       </c>
-      <c r="F4" s="85"/>
-      <c r="G4" s="86"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="84"/>
       <c r="H4" s="7">
         <v>2</v>
       </c>
@@ -11065,11 +11059,11 @@
       <c r="D5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="66">
-        <v>1</v>
-      </c>
-      <c r="F5" s="67"/>
-      <c r="G5" s="68"/>
+      <c r="E5" s="69">
+        <v>1</v>
+      </c>
+      <c r="F5" s="70"/>
+      <c r="G5" s="71"/>
       <c r="H5" s="7">
         <v>5</v>
       </c>
@@ -11134,11 +11128,11 @@
       <c r="D6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="84" t="s">
+      <c r="E6" s="82" t="s">
         <v>249</v>
       </c>
-      <c r="F6" s="85"/>
-      <c r="G6" s="86"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="84"/>
       <c r="H6" s="46">
         <v>29</v>
       </c>
@@ -11207,11 +11201,11 @@
       <c r="D7" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="81" t="s">
+      <c r="E7" s="85" t="s">
         <v>250</v>
       </c>
-      <c r="F7" s="82"/>
-      <c r="G7" s="83"/>
+      <c r="F7" s="86"/>
+      <c r="G7" s="87"/>
       <c r="H7" s="40">
         <v>19</v>
       </c>
@@ -11286,11 +11280,11 @@
       <c r="D8" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="78" t="s">
+      <c r="E8" s="88" t="s">
         <v>251</v>
       </c>
-      <c r="F8" s="79"/>
-      <c r="G8" s="80"/>
+      <c r="F8" s="89"/>
+      <c r="G8" s="90"/>
       <c r="H8" s="26">
         <v>3</v>
       </c>
@@ -11363,11 +11357,11 @@
       <c r="D9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="66" t="s">
+      <c r="E9" s="69" t="s">
         <v>234</v>
       </c>
-      <c r="F9" s="67"/>
-      <c r="G9" s="68"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="71"/>
       <c r="H9" s="46">
         <v>15</v>
       </c>
@@ -11446,11 +11440,11 @@
       <c r="D10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="66">
-        <v>1</v>
-      </c>
-      <c r="F10" s="67"/>
-      <c r="G10" s="68"/>
+      <c r="E10" s="69">
+        <v>1</v>
+      </c>
+      <c r="F10" s="70"/>
+      <c r="G10" s="71"/>
       <c r="H10" s="7">
         <v>2</v>
       </c>
@@ -11515,11 +11509,11 @@
       <c r="D11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="66" t="s">
+      <c r="E11" s="69" t="s">
         <v>166</v>
       </c>
-      <c r="F11" s="67"/>
-      <c r="G11" s="68"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="71"/>
       <c r="H11" s="7" t="s">
         <v>159</v>
       </c>
@@ -11580,11 +11574,11 @@
       <c r="D12" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="66" t="s">
+      <c r="E12" s="69" t="s">
         <v>252</v>
       </c>
-      <c r="F12" s="67"/>
-      <c r="G12" s="68"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="71"/>
       <c r="H12" s="7">
         <v>1</v>
       </c>
@@ -11651,11 +11645,11 @@
       <c r="D13" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="69">
-        <v>1</v>
-      </c>
-      <c r="F13" s="70"/>
-      <c r="G13" s="71"/>
+      <c r="E13" s="72">
+        <v>1</v>
+      </c>
+      <c r="F13" s="73"/>
+      <c r="G13" s="74"/>
       <c r="H13" s="31">
         <v>8</v>
       </c>
@@ -11726,11 +11720,11 @@
       <c r="D14" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="60" t="s">
+      <c r="E14" s="63" t="s">
         <v>253</v>
       </c>
-      <c r="F14" s="61"/>
-      <c r="G14" s="62"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="65"/>
       <c r="H14" s="26">
         <v>3</v>
       </c>
@@ -11801,11 +11795,11 @@
       <c r="D15" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="63">
+      <c r="E15" s="66">
         <v>13</v>
       </c>
-      <c r="F15" s="64"/>
-      <c r="G15" s="65"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="68"/>
       <c r="H15" s="46">
         <v>18</v>
       </c>
@@ -11882,11 +11876,11 @@
       <c r="D16" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="66">
+      <c r="E16" s="69">
         <v>4</v>
       </c>
-      <c r="F16" s="67"/>
-      <c r="G16" s="68"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="71"/>
       <c r="H16" s="7">
         <v>6</v>
       </c>
@@ -11955,11 +11949,11 @@
       <c r="D17" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="69">
+      <c r="E17" s="72">
         <v>4</v>
       </c>
-      <c r="F17" s="70"/>
-      <c r="G17" s="71"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="74"/>
       <c r="H17" s="21">
         <v>1</v>
       </c>
@@ -12020,11 +12014,11 @@
       <c r="D18" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="E18" s="72">
+      <c r="E18" s="75">
         <v>147</v>
       </c>
-      <c r="F18" s="73"/>
-      <c r="G18" s="74"/>
+      <c r="F18" s="76"/>
+      <c r="G18" s="77"/>
       <c r="H18" s="36">
         <v>119</v>
       </c>
@@ -12127,34 +12121,34 @@
       <c r="AC19" s="6"/>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="J20" s="90" t="s">
+      <c r="J20" s="62" t="s">
         <v>266</v>
       </c>
-      <c r="K20" s="90"/>
-      <c r="L20" s="90"/>
-      <c r="M20" s="90"/>
-      <c r="N20" s="90"/>
-      <c r="O20" s="90"/>
+      <c r="K20" s="62"/>
+      <c r="L20" s="62"/>
+      <c r="M20" s="62"/>
+      <c r="N20" s="62"/>
+      <c r="O20" s="62"/>
       <c r="AB20" s="6"/>
       <c r="AC20" s="6"/>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="J21" s="90"/>
-      <c r="K21" s="90"/>
-      <c r="L21" s="90"/>
-      <c r="M21" s="90"/>
-      <c r="N21" s="90"/>
-      <c r="O21" s="90"/>
+      <c r="J21" s="62"/>
+      <c r="K21" s="62"/>
+      <c r="L21" s="62"/>
+      <c r="M21" s="62"/>
+      <c r="N21" s="62"/>
+      <c r="O21" s="62"/>
       <c r="AB21" s="6"/>
       <c r="AC21" s="6"/>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="J22" s="90"/>
-      <c r="K22" s="90"/>
-      <c r="L22" s="90"/>
-      <c r="M22" s="90"/>
-      <c r="N22" s="90"/>
-      <c r="O22" s="90"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="62"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="62"/>
+      <c r="O22" s="62"/>
       <c r="AB22" s="6"/>
       <c r="AC22" s="6"/>
     </row>
@@ -12200,6 +12194,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="E5:G5"/>
     <mergeCell ref="E1:AM1"/>
     <mergeCell ref="J20:O22"/>
     <mergeCell ref="E14:G14"/>
@@ -12212,11 +12211,6 @@
     <mergeCell ref="E11:G11"/>
     <mergeCell ref="E12:G12"/>
     <mergeCell ref="E13:G13"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="E5:G5"/>
     <mergeCell ref="E6:G6"/>
     <mergeCell ref="E7:G7"/>
     <mergeCell ref="E8:G8"/>
